--- a/diseases/d107/2000-2004.xlsx
+++ b/diseases/d107/2000-2004.xlsx
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -17595,7 +17595,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21336,7 +21336,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -22583,7 +22583,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -23830,7 +23830,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -25077,7 +25077,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -26324,7 +26324,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -27571,7 +27571,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -28818,7 +28818,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -30065,7 +30065,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -31944,7 +31944,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -33191,7 +33191,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -34438,7 +34438,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -36932,7 +36932,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -38179,7 +38179,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -39426,7 +39426,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -40673,7 +40673,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -41920,7 +41920,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -43167,7 +43167,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -44414,7 +44414,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -45661,7 +45661,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -47540,7 +47540,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -48935,7 +48935,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -50330,7 +50330,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -51725,7 +51725,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -53120,7 +53120,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -54515,7 +54515,7 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN300" t="b">
@@ -55910,7 +55910,7 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN308" t="b">
@@ -57305,7 +57305,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -58700,7 +58700,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN324" t="b">
@@ -60095,7 +60095,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -61490,7 +61490,7 @@
       </c>
       <c r="AM340" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN340" t="b">
@@ -62885,7 +62885,7 @@
       </c>
       <c r="AM348" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN348" t="b">
@@ -64912,7 +64912,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -66307,7 +66307,7 @@
       </c>
       <c r="AM367" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN367" t="b">
@@ -67702,7 +67702,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -69097,7 +69097,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN383" t="b">
@@ -70492,7 +70492,7 @@
       </c>
       <c r="AM391" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN391" t="b">
@@ -71887,7 +71887,7 @@
       </c>
       <c r="AM399" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN399" t="b">
@@ -73282,7 +73282,7 @@
       </c>
       <c r="AM407" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN407" t="b">
@@ -74677,7 +74677,7 @@
       </c>
       <c r="AM415" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN415" t="b">
@@ -76072,7 +76072,7 @@
       </c>
       <c r="AM423" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN423" t="b">
@@ -77467,7 +77467,7 @@
       </c>
       <c r="AM431" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN431" t="b">
@@ -78862,7 +78862,7 @@
       </c>
       <c r="AM439" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN439" t="b">
@@ -80257,7 +80257,7 @@
       </c>
       <c r="AM447" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN447" t="b">
